--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488073_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488073_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7625</v>
+        <v>4.0308</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6724</v>
+        <v>5.7161</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9099</v>
+        <v>-1.6853</v>
       </c>
       <c r="G2" t="n">
         <v>0.8214</v>
@@ -610,13 +610,13 @@
         <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1065</v>
+        <v>1.3748</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3239</v>
+        <v>1.3676</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2174</v>
+        <v>0.0072</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9405</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2243</v>
+        <v>3.3096</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8042</v>
+        <v>3.9959</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5799</v>
+        <v>-0.6863</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8959</v>
+        <v>3.3981</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.1437</v>
       </c>
       <c r="I3" t="n">
-        <v>0.352</v>
+        <v>3.2544</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5564</v>
+        <v>3.9824</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1463</v>
+        <v>0.2018</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4101</v>
+        <v>3.7806</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6605</v>
+        <v>-0.5843</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6024</v>
+        <v>-0.0581</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0581</v>
+        <v>-0.5262</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5947</v>
+        <v>0.5947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3787</v>
+        <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6566</v>
+        <v>0.524</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7475</v>
+        <v>0.4011</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9091</v>
+        <v>0.1229</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2666</v>
+        <v>-1.2071</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4737</v>
+        <v>0.6036</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2071</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6527</v>
+        <v>3.0161</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2828</v>
+        <v>3.7027</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6301</v>
+        <v>-0.6865</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3981</v>
+        <v>-2.1127</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1437</v>
+        <v>1.8283</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2544</v>
+        <v>-3.941</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9824</v>
+        <v>0.35</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2018</v>
+        <v>2.8254</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7806</v>
+        <v>-2.4755</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5843</v>
+        <v>-2.4627</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0581</v>
+        <v>-0.9971</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5262</v>
+        <v>-1.4656</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5947</v>
+        <v>1.9822</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1329</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.312</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1791</v>
+        <v>0.0605</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2071</v>
+        <v>2.4142</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6036</v>
+        <v>2.6808</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8107</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3279</v>
+        <v>2.3729</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2952</v>
+        <v>3.3178</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9673</v>
+        <v>-0.9449</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1127</v>
+        <v>0.8959</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8283</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.941</v>
+        <v>0.352</v>
       </c>
       <c r="J5" t="n">
-        <v>0.35</v>
+        <v>3.5564</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8254</v>
+        <v>2.1463</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.4755</v>
+        <v>1.4101</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4627</v>
+        <v>-2.6605</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9971</v>
+        <v>-1.6024</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4656</v>
+        <v>-1.0581</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9822</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9822</v>
+        <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0441</v>
+        <v>1.8051</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2644</v>
+        <v>1.261</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2203</v>
+        <v>0.5441</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4142</v>
+        <v>0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6808</v>
+        <v>1.4737</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7689</v>
+        <v>2.2232</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0579</v>
+        <v>3.6526</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.289</v>
+        <v>-1.4294</v>
       </c>
       <c r="G6" t="n">
         <v>0.9507</v>
@@ -922,13 +922,13 @@
         <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0936</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1651</v>
+        <v>0.4295</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2587</v>
+        <v>0.1183</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2666</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7521</v>
+        <v>1.8145</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2024</v>
+        <v>4.2648</v>
       </c>
       <c r="F7" t="n">
         <v>-2.4504</v>
@@ -1000,10 +1000,10 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5433</v>
+        <v>0.6057</v>
       </c>
       <c r="T7" t="n">
-        <v>0.503</v>
+        <v>0.5654</v>
       </c>
       <c r="U7" t="n">
         <v>0.0403</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.508</v>
+        <v>1.7955</v>
       </c>
       <c r="E8" t="n">
-        <v>1.508</v>
+        <v>2.4573</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.508</v>
+        <v>1.1108</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3027</v>
+        <v>0.5177</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2053</v>
+        <v>0.5931</v>
       </c>
       <c r="J8" t="n">
-        <v>1.508</v>
+        <v>2.8266</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3027</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2053</v>
+        <v>2.053</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-1.7158</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.256</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1.4599</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.6341</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.3553</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.2789</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.469</v>
+        <v>1.508</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3555</v>
+        <v>1.508</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8864</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1108</v>
+        <v>1.508</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5177</v>
+        <v>0.3027</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5931</v>
+        <v>1.2053</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8266</v>
+        <v>1.508</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.3027</v>
       </c>
       <c r="L9" t="n">
-        <v>2.053</v>
+        <v>1.2053</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7158</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.256</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4599</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3076</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2534</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0543</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3486</v>
+        <v>0.8737</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6402</v>
+        <v>2.9687</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2916</v>
+        <v>-2.095</v>
       </c>
       <c r="G11" t="n">
         <v>-2.206</v>
@@ -1312,13 +1312,13 @@
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2265</v>
+        <v>0.7516</v>
       </c>
       <c r="T11" t="n">
-        <v>0.503</v>
+        <v>0.8315</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2764</v>
+        <v>-0.0799</v>
       </c>
       <c r="V11" t="n">
         <v>0.9405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1499</v>
+        <v>0.7383</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6858</v>
+        <v>2.2181</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.536</v>
+        <v>-1.4798</v>
       </c>
       <c r="G12" t="n">
         <v>2.152</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0485</v>
+        <v>0.6369</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1065</v>
+        <v>0.6388</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0581</v>
+        <v>-0.0019</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2666</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.12</v>
+        <v>-0.1627</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9911</v>
+        <v>2.2572</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1111</v>
+        <v>-2.4199</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4867</v>
@@ -1468,13 +1468,13 @@
         <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9614</v>
+        <v>0.9186</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4626</v>
+        <v>0.7288</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4987</v>
+        <v>0.1899</v>
       </c>
       <c r="V13" t="n">
         <v>1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.3649</v>
+        <v>-1.3754</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3914</v>
+        <v>-0.2895</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9736</v>
+        <v>-1.0859</v>
       </c>
       <c r="G14" t="n">
         <v>-1.8113</v>
@@ -1546,13 +1546,13 @@
         <v>0.1982</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2481</v>
+        <v>0.2377</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1469</v>
+        <v>0.2487</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1013</v>
+        <v>-0.011</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.8401</v>
+        <v>-2.5698</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2902</v>
+        <v>0.5605</v>
       </c>
       <c r="F15" t="n">
         <v>-3.1303</v>
@@ -1624,10 +1624,10 @@
         <v>1.784</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7254</v>
+        <v>0.9958</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8209</v>
+        <v>1.0913</v>
       </c>
       <c r="U15" t="n">
         <v>-0.0955</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>17.5442</v>
+        <v>18.48</v>
       </c>
       <c r="E16" t="n">
-        <v>36.29960000000001</v>
+        <v>37.2355</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.7556</v>
+        <v>-18.7555</v>
       </c>
       <c r="G16" t="n">
         <v>2.260200000000002</v>
@@ -1693,7 +1693,7 @@
         <v>-17.3154</v>
       </c>
       <c r="P16" t="n">
-        <v>7.928800000000003</v>
+        <v>7.928799999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>-10.9021</v>
@@ -1702,10 +1702,10 @@
         <v>18.8311</v>
       </c>
       <c r="S16" t="n">
-        <v>8.8287</v>
+        <v>9.764600000000002</v>
       </c>
       <c r="T16" t="n">
-        <v>7.654999999999999</v>
+        <v>8.5909</v>
       </c>
       <c r="U16" t="n">
         <v>1.1738</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7756</v>
+        <v>2.9337</v>
       </c>
       <c r="E17" t="n">
-        <v>5.6181</v>
+        <v>5.3125</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8425</v>
+        <v>-2.3789</v>
       </c>
       <c r="G17" t="n">
         <v>0.119</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5683</v>
+        <v>-0.4102</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.2394</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6345</v>
+        <v>-0.1708</v>
       </c>
       <c r="V17" t="n">
         <v>3.6213</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1638</v>
+        <v>1.8299</v>
       </c>
       <c r="E18" t="n">
-        <v>6.3589</v>
+        <v>6.257</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.1951</v>
+        <v>-4.4271</v>
       </c>
       <c r="G18" t="n">
         <v>3.9907</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2378</v>
+        <v>-0.5717</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>-0.1715</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1682</v>
+        <v>-0.4002</v>
       </c>
       <c r="V18" t="n">
         <v>-2.5802</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4024</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2838</v>
+        <v>1.3857</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8814</v>
+        <v>-0.8298</v>
       </c>
       <c r="G20" t="n">
         <v>0.4806</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.0752</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0158</v>
+        <v>0.0358</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0258</v>
+        <v>-0.1617</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0561</v>
+        <v>-0.3514</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0819</v>
+        <v>0.1897</v>
       </c>
       <c r="G21" t="n">
         <v>-0.213</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1872</v>
+        <v>0.0514</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5543</v>
+        <v>0.1469</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3671</v>
+        <v>-0.0955</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7773</v>
+        <v>-0.7492</v>
       </c>
       <c r="E22" t="n">
         <v>0.2182</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.9674</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6602</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3153</v>
+        <v>-0.2873</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1905</v>
+        <v>-0.1625</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5189</v>
+        <v>-1.1101</v>
       </c>
       <c r="E23" t="n">
-        <v>3.1288</v>
+        <v>3.4345</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.6477</v>
+        <v>-4.5446</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2062</v>
@@ -2248,13 +2248,13 @@
         <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.898</v>
+        <v>-0.4892</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3523</v>
+        <v>-0.0467</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5456</v>
+        <v>-0.4425</v>
       </c>
       <c r="V23" t="n">
         <v>1.3781</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7685</v>
+        <v>-1.2885</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6802</v>
+        <v>2.8839</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.4487</v>
+        <v>-4.1724</v>
       </c>
       <c r="G24" t="n">
         <v>2.301</v>
@@ -2326,13 +2326,13 @@
         <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2426</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1651</v>
+        <v>0.0386</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0775</v>
+        <v>-0.8013</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8358</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3766</v>
+        <v>-2.7477</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3259</v>
+        <v>1.6315</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.7025</v>
+        <v>-4.3793</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8746</v>
@@ -2404,13 +2404,13 @@
         <v>1.784</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6237</v>
+        <v>-0.9948</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8001</v>
+        <v>-0.4945</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8235</v>
+        <v>-0.5003</v>
       </c>
       <c r="V25" t="n">
         <v>3.2843</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.5984</v>
+        <v>-4.287</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5293</v>
+        <v>-0.733</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.0692</v>
+        <v>-3.5539</v>
       </c>
       <c r="G26" t="n">
         <v>-3.15</v>
@@ -2482,13 +2482,13 @@
         <v>1.784</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9585</v>
+        <v>-0.647</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0586</v>
+        <v>-0.2623</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8999</v>
+        <v>-0.3846</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2917</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.3411</v>
+        <v>-5.0119</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1897</v>
+        <v>0.0878</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.5307</v>
+        <v>-5.0997</v>
       </c>
       <c r="G27" t="n">
         <v>-0.6392</v>
@@ -2560,13 +2560,13 @@
         <v>1.784</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.0477</v>
+        <v>-0.7186</v>
       </c>
       <c r="T27" t="n">
-        <v>0.0772</v>
+        <v>-0.0246</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.1249</v>
+        <v>-0.694</v>
       </c>
       <c r="V27" t="n">
         <v>-1.4737</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.3847</v>
+        <v>-5.017</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.4803</v>
+        <v>-2.2766</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.9044</v>
+        <v>-2.7405</v>
       </c>
       <c r="G28" t="n">
         <v>-3.3137</v>
@@ -2638,13 +2638,13 @@
         <v>0.5947</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.0458</v>
+        <v>-0.6782</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.2386</v>
+        <v>-0.0348</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.8073</v>
+        <v>-0.6434</v>
       </c>
       <c r="V28" t="n">
         <v>-0.6287</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-17.5442</v>
+        <v>-14.1483</v>
       </c>
       <c r="E29" t="n">
         <v>18.7554</v>
       </c>
       <c r="F29" t="n">
-        <v>-36.29960000000001</v>
+        <v>-32.90389999999999</v>
       </c>
       <c r="G29" t="n">
         <v>-2.2603</v>
@@ -2716,13 +2716,13 @@
         <v>10.9022</v>
       </c>
       <c r="S29" t="n">
-        <v>-8.8287</v>
+        <v>-5.433000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.1738</v>
+        <v>-1.1736</v>
       </c>
       <c r="U29" t="n">
-        <v>-7.654799999999999</v>
+        <v>-4.2593</v>
       </c>
       <c r="V29" t="n">
         <v>1.4736</v>
